--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -1,92 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Option 1\Test_automation_Option 1\Test_automation_Option 1\test_automation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02121B89-E3DB-4032-8CF4-2C2976BCAEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
+    <sheet name=" Test cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Input length type</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Expected output</t>
-  </si>
-  <si>
-    <t>Actual output</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8.5"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -133,46 +111,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,105 +484,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col width="10.88671875" customWidth="1" min="1" max="1"/>
+    <col width="22.109375" customWidth="1" min="3" max="3"/>
+    <col width="25.33203125" customWidth="1" min="4" max="4"/>
+    <col width="22.5546875" customWidth="1" min="5" max="5"/>
+    <col width="14.33203125" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12.33203125" customWidth="1" min="9" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+    <row r="1" ht="36.6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input length type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected output</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Actual output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="49.95" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>POS_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>mama oyata aadharei</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>මම ඔයාට ආදරෙයි</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>මම ඔයාට ආදරෙයි</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="49.95" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="49.95" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="49.95" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="49.95" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>POS_0002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Jepponta Pissu</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ජෙප්පොන්ට පිස්සු</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>ජෙප්පෝන්ට පිස්සු</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="49.95" customHeight="1">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="49.95" customHeight="1">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="49.95" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="49.95" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>POS_0003</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>NDM eka amarui</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>NDM එක අමාරුයි</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>NDM ඒක අමාරුයි</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="49.95" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="49.95" customHeight="1">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="49.95" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="C6:C9"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="C2:C5"/>
@@ -546,9 +713,14 @@
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="F6:F9"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="C10:C13"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="E10:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>https://courseweb.ස්ලිට්.ල්ක්/ මේකෙන් ගිහින් බලන්න</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>ඒක මාරු විහිළුව 😅😅😅😅</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>ඔයාට මාත් එක්ක තියන ප්‍රශ්නය මොකක්ද?</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>මං කියන විදිහට ඉන්න බැරි නම් ආයෙ එන්න එපා</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>happy new year</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>please මට බනින්න එපා</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>ඔව් මට ඒක තේරුණා</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>එල එල එහෙම තමයි ඉන්න ඕනේ</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>වැඩේ එළකිරි මචන්</t>
+          <t>කවදාහරි දවසක මම නැති උනොත් ඔයාට තනියෙන් ජිවත් වෙන්න පුලුවන්ද?</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,12 +48,6 @@
       <family val="2"/>
       <color theme="1"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -131,7 +125,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,10 +149,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -505,8 +499,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
+  <dimension ref="A1:F201"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="1" max="1"/>
     <col width="22.109375" customWidth="1" min="3" max="3"/>
@@ -552,7 +546,7 @@
     <row r="2" ht="49.95" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>POS_0001</t>
+          <t>Neg_0001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -562,7 +556,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mama oyata adareyi</t>
+          <t>mama oyata adarei</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -570,14 +564,10 @@
           <t>මම ඔයාට ආදරෙයි</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>මම ඔයාට ආදරෙයි</t>
-        </is>
-      </c>
+      <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -608,7 +598,7 @@
     <row r="6" ht="49.95" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>POS_0002</t>
+          <t>Neg_0002</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -664,7 +654,7 @@
     <row r="10" ht="49.95" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>POS_0003</t>
+          <t>Neg_0003</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -720,7 +710,7 @@
     <row r="14" ht="49.95" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>POS_0004</t>
+          <t>Neg_0004</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -776,12 +766,12 @@
     <row r="18" ht="49.95" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>POS_0005</t>
+          <t>Neg_0005</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -832,7 +822,7 @@
     <row r="22" ht="49.95" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>POS_0006</t>
+          <t>Neg_0006</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -888,7 +878,7 @@
     <row r="26" ht="49.95" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>POS_0007</t>
+          <t>Neg_0007</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -898,7 +888,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>suba udaesanak wewa</t>
+          <t>suba udasanak wewa</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -944,7 +934,7 @@
     <row r="30" ht="49.95" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>POS_0008</t>
+          <t>Neg_0008</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -959,7 +949,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>කරුණාකරලා මට උදව් කරන්න</t>
+          <t>කරුනාකරලා මට උදව් කරන්න</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1000,7 +990,7 @@
     <row r="34" ht="49.95" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>POS_0009</t>
+          <t>Neg_0009</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1056,7 +1046,7 @@
     <row r="38" ht="49.95" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>POS_0010</t>
+          <t>Neg_0010</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1066,12 +1056,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>hari hari eka karamu</t>
+          <t>hari hari eka hodai</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>හරි හරි ඒක කරමු</t>
+          <t>හරි හරි ඒක හොදයි</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1112,7 +1102,7 @@
     <row r="42" ht="49.95" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>POS_0011</t>
+          <t>Neg_0011</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1168,7 +1158,7 @@
     <row r="46" ht="49.95" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>POS_0012</t>
+          <t>Neg_0012</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1224,7 +1214,7 @@
     <row r="50" ht="49.95" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>POS_0013</t>
+          <t>Neg_0013</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1280,7 +1270,7 @@
     <row r="54" ht="49.95" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>POS_0014</t>
+          <t>Neg_0014</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1336,7 +1326,7 @@
     <row r="58" ht="49.95" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>POS_0015</t>
+          <t>Neg_0015</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1392,7 +1382,7 @@
     <row r="62" ht="49.95" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>POS_0016</t>
+          <t>Neg_0016</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1448,7 +1438,7 @@
     <row r="66" ht="49.95" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>POS_0017</t>
+          <t>Neg_0017</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1473,7 +1463,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1494,7 @@
     <row r="70" ht="49.95" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>POS_0018</t>
+          <t>Neg_0018</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -1560,7 +1550,7 @@
     <row r="74" ht="49.95" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>POS_0019</t>
+          <t>Neg_0019</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -1612,7 +1602,7 @@
     <row r="78" ht="49.95" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>POS_0020</t>
+          <t>Neg_0020</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -1668,7 +1658,7 @@
     <row r="82" ht="49.95" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>POS_0021</t>
+          <t>Neg_0021</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -1724,7 +1714,7 @@
     <row r="86" ht="49.95" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>POS_0022</t>
+          <t>Neg_0022</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -1749,7 +1739,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1770,7 @@
     <row r="90" ht="49.95" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>POS_0023</t>
+          <t>Neg_0023</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -1800,7 +1790,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>ඔයා මට Rs.500 නයයි</t>
+          <t>අද Exhibition එකේ 2nd day එක</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -1836,7 +1826,7 @@
     <row r="94" ht="49.95" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>POS_0024</t>
+          <t>Neg_0024</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -1846,7 +1836,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>mage upandhinaya 2002-10-12</t>
+          <t>mage upandinaya 2002-10-12</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -1892,7 +1882,7 @@
     <row r="98" ht="49.95" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>POS_0025</t>
+          <t>Neg_0025</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -1917,7 +1907,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1938,7 @@
     <row r="102" ht="49.95" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>POS_0026</t>
+          <t>Neg_0026</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -1968,7 +1958,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>ඔයා එද්දි සීනි 1kg අරන් එන්න</t>
+          <t>හෙට උදේ 7.30a.ම්. වැඩ්ධි එන්න</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -2004,7 +1994,7 @@
     <row r="106" ht="49.95" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>POS_0027</t>
+          <t>Neg_0027</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -2060,7 +2050,7 @@
     <row r="110" ht="49.95" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>POS_0028</t>
+          <t>Neg_0028</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -2073,7 +2063,7 @@
           <t xml:space="preserve"> https://courseweb.sliit.lk/ meken gihin balanna</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>https://courseweb.sliit.lk/  මේකෙන් ගිහින් බලන්න</t>
         </is>
@@ -2085,7 +2075,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2106,7 @@
     <row r="114" ht="49.95" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>POS_0029</t>
+          <t>Neg_0029</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -2129,7 +2119,7 @@
           <t>eka maru wihiluwa 😅😅😅😅</t>
         </is>
       </c>
-      <c r="D114" s="10" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>ඒක මරු විහිලුව😅😅😅😅</t>
         </is>
@@ -2172,12 +2162,12 @@
     <row r="118" ht="49.95" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>POS_0030</t>
+          <t>Neg_0030</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2185,7 +2175,7 @@
           <t>oyata math ekka thiyana prashnaya mokakda?</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>ඔයාට මාත් එක්ක තියන ප්‍රශ්නය මොකක්ද?</t>
         </is>
@@ -2197,7 +2187,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2218,12 @@
     <row r="122" ht="49.95" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>POS_0031</t>
+          <t>Neg_0031</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2284,7 +2274,7 @@
     <row r="126" ht="49.95" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>POS_0032</t>
+          <t>Neg_0032</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -2340,7 +2330,7 @@
     <row r="130" ht="49.95" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>POS_0033</t>
+          <t>Neg_0033</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -2365,7 +2355,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2386,7 @@
     <row r="134" ht="49.95" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>POS_0034</t>
+          <t>Neg_0034</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -2411,7 +2401,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>ඔව් මට ඒක තේරුණා</t>
+          <t>ඔව් මට ඒක තේරුනා</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -2452,7 +2442,7 @@
     <row r="138" ht="49.95" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>POS_0035</t>
+          <t>Neg_0035</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -2508,12 +2498,12 @@
     <row r="142" ht="49.95" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>POS_0036</t>
+          <t>Neg_0036</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -2533,7 +2523,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2554,7 @@
     <row r="146" ht="49.95" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>POS_0037</t>
+          <t>Neg_0037</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -2574,22 +2564,18 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>kavadahari dhavasaka mama nathi unoth oyata thaniyen jivath wenna puluwanda?</t>
+          <t>api dinner ekata ada eliyata yamu</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>කවදාහරි දවසක මම නැති උනොත් ඔයාට තනියම ජීවත් වෙන්න පුලුවන්ද?</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>වැඩේ එළකිරි මචන්</t>
-        </is>
-      </c>
+          <t>අපි ඩිනර් එකට අද එලියට යමු</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="n"/>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2606,7 @@
     <row r="150" ht="49.95" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>POS_0038</t>
+          <t>Neg_0038</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -2630,22 +2616,18 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>kavadahari dhavasaka mama nathi unoth oyata thaniyen jivath wenna puluwanda?</t>
+          <t>what are you doing right now?</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>කවදාහරි දවසක මම නැති උනොත් ඔයාට තනියම ජීවත් වෙන්න පුලුවන්ද?</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>වැඩේ එළකිරි මචන්</t>
-        </is>
-      </c>
+          <t>ඔයා මොකද දැන් කරන්නේ?</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="n"/>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2673,51 +2655,735 @@
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
     </row>
+    <row r="154" ht="49.95" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0039</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>mage wifi eka iawara wela mokuth karaganna widhihak nAA</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>මගේ වයිෆයි එක ඉවර වෙලා මොකුත් කරගන්න විදිහක් නෑ</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="49.95" customHeight="1">
+      <c r="A155" s="3" t="n"/>
+      <c r="B155" s="3" t="n"/>
+      <c r="C155" s="3" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n"/>
+    </row>
+    <row r="156" ht="49.95" customHeight="1">
+      <c r="A156" s="3" t="n"/>
+      <c r="B156" s="3" t="n"/>
+      <c r="C156" s="3" t="n"/>
+      <c r="D156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="3" t="n"/>
+    </row>
+    <row r="157" ht="49.95" customHeight="1">
+      <c r="A157" s="4" t="n"/>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
+    </row>
+    <row r="158" ht="49.95" customHeight="1">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0040</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>api mulinma instagram eken thamayi kathabaha kale</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>අපි මුලින්ම ඉන්ස්ටග්‍රෑම් එකෙන් තමයි කතාබහ කලේ</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="49.95" customHeight="1">
+      <c r="A159" s="3" t="n"/>
+      <c r="B159" s="3" t="n"/>
+      <c r="C159" s="3" t="n"/>
+      <c r="D159" s="3" t="n"/>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n"/>
+    </row>
+    <row r="160" ht="49.95" customHeight="1">
+      <c r="A160" s="3" t="n"/>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+    </row>
+    <row r="161" ht="49.95" customHeight="1">
+      <c r="A161" s="4" t="n"/>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+    </row>
+    <row r="162" ht="49.95" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0041</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>oyata man karanna dhunnu wAde karala dhenna ASAP</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>ඔයාට මං කරන්න දුන්නු වැඩේ කරලා දෙන්න ASAP</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="49.95" customHeight="1">
+      <c r="A163" s="3" t="n"/>
+      <c r="B163" s="3" t="n"/>
+      <c r="C163" s="3" t="n"/>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n"/>
+    </row>
+    <row r="164" ht="49.95" customHeight="1">
+      <c r="A164" s="3" t="n"/>
+      <c r="B164" s="3" t="n"/>
+      <c r="C164" s="3" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n"/>
+    </row>
+    <row r="165" ht="49.95" customHeight="1">
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="n"/>
+    </row>
+    <row r="166" ht="49.95" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0042</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>ada lab ekedi mata mara wAdak thama wune</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>අද ලැබ් එකේදි මට මාර වැඩක් තමා වුනේ</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="49.95" customHeight="1">
+      <c r="A167" s="3" t="n"/>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="3" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n"/>
+    </row>
+    <row r="168" ht="49.95" customHeight="1">
+      <c r="A168" s="3" t="n"/>
+      <c r="B168" s="3" t="n"/>
+      <c r="C168" s="3" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n"/>
+    </row>
+    <row r="169" ht="49.95" customHeight="1">
+      <c r="A169" s="4" t="n"/>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="n"/>
+    </row>
+    <row r="170" ht="49.95" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0043</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>oya colombo hitiya nam api dennata awidhinna yanna thibuna</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>ඔයා කොළඹ හිටියා නම් අපි දෙන්නට ඇවිදින්න යන්න තිබ්බා</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="49.95" customHeight="1">
+      <c r="A171" s="3" t="n"/>
+      <c r="B171" s="3" t="n"/>
+      <c r="C171" s="3" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n"/>
+    </row>
+    <row r="172" ht="49.95" customHeight="1">
+      <c r="A172" s="3" t="n"/>
+      <c r="B172" s="3" t="n"/>
+      <c r="C172" s="3" t="n"/>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n"/>
+    </row>
+    <row r="173" ht="49.95" customHeight="1">
+      <c r="A173" s="4" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="n"/>
+    </row>
+    <row r="174" ht="49.95" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0044</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>me awurudde april 14ta ape 3weni anniversary eka</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>මේ අවුරුද්දේ අප්‍රේල් 14ට අපි දෙන්නගේ 3 වෙනි සංවත්සරය</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="49.95" customHeight="1">
+      <c r="A175" s="3" t="n"/>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n"/>
+    </row>
+    <row r="176" ht="49.95" customHeight="1">
+      <c r="A176" s="3" t="n"/>
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+    </row>
+    <row r="177" ht="49.95" customHeight="1">
+      <c r="A177" s="4" t="n"/>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="n"/>
+    </row>
+    <row r="178" ht="49.95" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0045</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>man hAmadhama udheta kilometer 5k awidhinna yanna hithagena innawa</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>මං හැමදාම උදේට කිලෝමීටර් 5ක් ඇවිදින්න යන්න හිතාගෙන ඉන්නවා</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="49.95" customHeight="1">
+      <c r="A179" s="3" t="n"/>
+      <c r="B179" s="3" t="n"/>
+      <c r="C179" s="3" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n"/>
+    </row>
+    <row r="180" ht="49.95" customHeight="1">
+      <c r="A180" s="3" t="n"/>
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+    </row>
+    <row r="181" ht="49.95" customHeight="1">
+      <c r="A181" s="4" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="n"/>
+    </row>
+    <row r="182" ht="49.95" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0046</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>ada api balamu rs. 5000n moanawadha apata kanna puluwan kiyala</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>අද අපි බලමු රු.5000න් අපට මොනවද කන්න පුලුවන් කියලා</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>වැඩේ එළකිරි මචන්</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="49.95" customHeight="1">
+      <c r="A183" s="3" t="n"/>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+    </row>
+    <row r="184" ht="49.95" customHeight="1">
+      <c r="A184" s="3" t="n"/>
+      <c r="B184" s="3" t="n"/>
+      <c r="C184" s="3" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n"/>
+    </row>
+    <row r="185" ht="49.95" customHeight="1">
+      <c r="A185" s="4" t="n"/>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="4" t="n"/>
+      <c r="F185" s="4" t="n"/>
+    </row>
+    <row r="186" ht="49.95" customHeight="1">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0047</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>jacob mula idalama boruwak kale kiyala mata nam hodatama theruna eya hAsirunu widihath ekka</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>ජාකොබ් මුල ඉදලම බොරුවක් කලේ කියලා මට නම් තේරුනා එයා හැසිරුනු විදිහත් එක්ක</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>ජකොබ් මුල ඉදලම බොරුවක් කලේ කියලා මට නම් හොදටම තේරුනා එයා හාසිරුණු විදිහත් එක්ක</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="49.95" customHeight="1">
+      <c r="A187" s="3" t="n"/>
+      <c r="B187" s="3" t="n"/>
+      <c r="C187" s="3" t="n"/>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n"/>
+      <c r="F187" s="3" t="n"/>
+    </row>
+    <row r="188" ht="49.95" customHeight="1">
+      <c r="A188" s="3" t="n"/>
+      <c r="B188" s="3" t="n"/>
+      <c r="C188" s="3" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="3" t="n"/>
+    </row>
+    <row r="189" ht="49.95" customHeight="1">
+      <c r="A189" s="4" t="n"/>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="4" t="n"/>
+      <c r="F189" s="4" t="n"/>
+    </row>
+    <row r="190" ht="49.95" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0048</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>mata nam me widihata idala epa wela thiyenne🙂🙂🙂🙂🙂</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>මට නම් මේ විදිහට ඉදලා එපා වෙලා තියෙන්නේ🙂🙂🙂🙂🙂</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>මට නම් මේ විදිහට ඉදලා එපා වෙලා තියෙන්නේ 😅😅😅😅😅😅</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="49.95" customHeight="1">
+      <c r="A191" s="3" t="n"/>
+      <c r="B191" s="3" t="n"/>
+      <c r="C191" s="3" t="n"/>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="3" t="n"/>
+      <c r="F191" s="3" t="n"/>
+    </row>
+    <row r="192" ht="49.95" customHeight="1">
+      <c r="A192" s="3" t="n"/>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+    </row>
+    <row r="193" ht="49.95" customHeight="1">
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="4" t="n"/>
+      <c r="F193" s="4" t="n"/>
+    </row>
+    <row r="194" ht="49.95" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0049</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>ubalata hena gahanawa apata mechchra wAda kandarawak dhenawata</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>උබලට හෙන ගහනවා අපට මෙච්චර වැඩ කන්දරාවක් දෙනවට</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>උබලට හෙන ගහනවා අපට මෙච්චර වද කන්දරාවක් දෙනවට</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="49.95" customHeight="1">
+      <c r="A195" s="3" t="n"/>
+      <c r="B195" s="3" t="n"/>
+      <c r="C195" s="3" t="n"/>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
+      <c r="F195" s="3" t="n"/>
+    </row>
+    <row r="196" ht="49.95" customHeight="1">
+      <c r="A196" s="3" t="n"/>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="3" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n"/>
+    </row>
+    <row r="197" ht="49.95" customHeight="1">
+      <c r="A197" s="4" t="n"/>
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="4" t="n"/>
+      <c r="D197" s="4" t="n"/>
+      <c r="E197" s="4" t="n"/>
+      <c r="F197" s="4" t="n"/>
+    </row>
+    <row r="198" ht="49.95" customHeight="1">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Neg_0050</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>ane wachanayk hari katha karannko pawan</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>අනෙ වචනයක් හරි කතා කරන්නකෝ පවන්</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>අනේ වචනයක් හරි කතා කරන්නකෝ පවන්</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="49.95" customHeight="1">
+      <c r="A199" s="3" t="n"/>
+      <c r="B199" s="3" t="n"/>
+      <c r="C199" s="3" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="3" t="n"/>
+      <c r="F199" s="3" t="n"/>
+    </row>
+    <row r="200" ht="49.95" customHeight="1">
+      <c r="A200" s="3" t="n"/>
+      <c r="B200" s="3" t="n"/>
+      <c r="C200" s="3" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n"/>
+    </row>
+    <row r="201" ht="49.95" customHeight="1">
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="228">
+  <mergeCells count="300">
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B66:B69"/>
     <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
     <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A162:A165"/>
     <mergeCell ref="F30:F33"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="E38:E41"/>
+    <mergeCell ref="C162:C165"/>
     <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B130:B133"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="D46:D49"/>
     <mergeCell ref="C54:C57"/>
+    <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
     <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="A178:A181"/>
     <mergeCell ref="D126:D129"/>
     <mergeCell ref="C94:C97"/>
     <mergeCell ref="A74:A77"/>
     <mergeCell ref="F126:F129"/>
+    <mergeCell ref="D166:D169"/>
     <mergeCell ref="E94:E97"/>
     <mergeCell ref="E90:E93"/>
     <mergeCell ref="F110:F113"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="D150:D153"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="F46:F49"/>
+    <mergeCell ref="B166:B169"/>
     <mergeCell ref="E74:E77"/>
     <mergeCell ref="B78:B81"/>
     <mergeCell ref="F42:F45"/>
     <mergeCell ref="B118:B121"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E154:E157"/>
     <mergeCell ref="E110:E113"/>
+    <mergeCell ref="A2:A5"/>
     <mergeCell ref="F94:F97"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B186:B189"/>
     <mergeCell ref="C82:C85"/>
     <mergeCell ref="D102:D105"/>
     <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
     <mergeCell ref="D142:D145"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
@@ -2725,9 +3391,9 @@
     <mergeCell ref="E26:E29"/>
     <mergeCell ref="D98:D101"/>
     <mergeCell ref="C66:C69"/>
-    <mergeCell ref="F98:F101"/>
     <mergeCell ref="A102:A105"/>
     <mergeCell ref="E66:E69"/>
+    <mergeCell ref="F98:F101"/>
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="B26:B29"/>
@@ -2740,6 +3406,7 @@
     <mergeCell ref="E130:E133"/>
     <mergeCell ref="D54:D57"/>
     <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B194:B197"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D50:D53"/>
@@ -2748,7 +3415,10 @@
     <mergeCell ref="F146:F149"/>
     <mergeCell ref="B122:B125"/>
     <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
     <mergeCell ref="D34:D37"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="F178:F181"/>
     <mergeCell ref="C42:C45"/>
     <mergeCell ref="F34:F37"/>
     <mergeCell ref="B18:B21"/>
@@ -2762,34 +3432,48 @@
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="E122:E125"/>
     <mergeCell ref="F18:F21"/>
+    <mergeCell ref="B170:B173"/>
     <mergeCell ref="E78:E81"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
     <mergeCell ref="B58:B61"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="C134:C137"/>
+    <mergeCell ref="E186:E189"/>
     <mergeCell ref="C114:C117"/>
+    <mergeCell ref="A154:A157"/>
     <mergeCell ref="F22:F25"/>
     <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E170:E173"/>
     <mergeCell ref="E114:E117"/>
     <mergeCell ref="C70:C73"/>
     <mergeCell ref="F102:F105"/>
     <mergeCell ref="E70:E73"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C46:C49"/>
     <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="F190:F193"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C138:C141"/>
+    <mergeCell ref="C178:C181"/>
     <mergeCell ref="E54:E57"/>
     <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E178:E181"/>
     <mergeCell ref="D62:D65"/>
     <mergeCell ref="D118:D121"/>
     <mergeCell ref="F62:F65"/>
+    <mergeCell ref="B198:B201"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
     <mergeCell ref="A130:A133"/>
+    <mergeCell ref="F182:F185"/>
     <mergeCell ref="D38:D41"/>
     <mergeCell ref="A82:A85"/>
     <mergeCell ref="B110:B113"/>
@@ -2798,10 +3482,14 @@
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="E146:E149"/>
     <mergeCell ref="A58:A61"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
     <mergeCell ref="C74:C77"/>
     <mergeCell ref="C126:C129"/>
+    <mergeCell ref="F162:F165"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="B94:B97"/>
+    <mergeCell ref="C166:C169"/>
     <mergeCell ref="E126:E129"/>
     <mergeCell ref="C58:C61"/>
     <mergeCell ref="E58:E61"/>
@@ -2809,12 +3497,18 @@
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B102:B105"/>
     <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
     <mergeCell ref="B98:B101"/>
     <mergeCell ref="A66:A69"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
     <mergeCell ref="A118:A121"/>
-    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F154:F157"/>
     <mergeCell ref="C118:C121"/>
-    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="D186:D189"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="C50:C53"/>
@@ -2828,21 +3522,26 @@
     <mergeCell ref="E46:E49"/>
     <mergeCell ref="D66:D69"/>
     <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
     <mergeCell ref="B146:B149"/>
-    <mergeCell ref="F66:F69"/>
     <mergeCell ref="D18:D21"/>
     <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B178:B181"/>
     <mergeCell ref="E86:E89"/>
     <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F50:F53"/>
     <mergeCell ref="B74:B77"/>
     <mergeCell ref="A42:A45"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="E162:E165"/>
     <mergeCell ref="D130:D133"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A134:A137"/>
+    <mergeCell ref="B162:B165"/>
     <mergeCell ref="F130:F133"/>
+    <mergeCell ref="C194:C197"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
     <mergeCell ref="A62:A65"/>
@@ -2851,19 +3550,27 @@
     <mergeCell ref="C122:C125"/>
     <mergeCell ref="C78:C81"/>
     <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
     <mergeCell ref="D94:D97"/>
     <mergeCell ref="E142:E145"/>
     <mergeCell ref="C18:C21"/>
+    <mergeCell ref="E194:E197"/>
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B150:B153"/>
-    <mergeCell ref="E18:E21"/>
     <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
     <mergeCell ref="D22:D25"/>
     <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
     <mergeCell ref="F78:F81"/>
     <mergeCell ref="F118:F121"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
     <mergeCell ref="B86:B89"/>
     <mergeCell ref="A138:A141"/>
     <mergeCell ref="E82:E85"/>
@@ -2880,26 +3587,41 @@
     <mergeCell ref="E98:E101"/>
     <mergeCell ref="F70:F73"/>
     <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
     <mergeCell ref="D134:D137"/>
+    <mergeCell ref="D194:D197"/>
     <mergeCell ref="F134:F137"/>
     <mergeCell ref="E62:E65"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="C198:C201"/>
     <mergeCell ref="D122:D125"/>
     <mergeCell ref="C90:C93"/>
     <mergeCell ref="A126:A129"/>
+    <mergeCell ref="D162:D165"/>
     <mergeCell ref="C130:C133"/>
     <mergeCell ref="F122:F125"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="F186:F189"/>
     <mergeCell ref="C150:C153"/>
+    <mergeCell ref="C190:C193"/>
     <mergeCell ref="B114:B117"/>
     <mergeCell ref="E22:E25"/>
     <mergeCell ref="D74:D77"/>
     <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
     <mergeCell ref="B138:B141"/>
     <mergeCell ref="E134:E137"/>
     <mergeCell ref="D138:D141"/>
     <mergeCell ref="F54:F57"/>
-    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="C158:C161"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="A98:A101"/>
@@ -2907,7 +3629,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" display="https://courseweb.sliit.lk/ මේකෙන් ගිහින් බලන්න" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" display="https://courseweb.sliit.lk/ මේකෙන් ගිහින් බලන්න" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
